--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -1319,7 +1319,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>F02</v>
+        <v>F02_TC01</v>
       </c>
       <c r="D6" t="str">
         <v>1</v>
@@ -1345,7 +1345,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>F02</v>
+        <v>F02_TC02</v>
       </c>
       <c r="D7" t="str">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>F02</v>
+        <v>F02_TC03</v>
       </c>
       <c r="D8" t="str">
         <v>-5</v>
@@ -1397,7 +1397,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>F02</v>
+        <v>F02_TC04</v>
       </c>
       <c r="D9" t="str">
         <v>1</v>
@@ -1423,7 +1423,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="str">
-        <v>F02</v>
+        <v>F02_TC05</v>
       </c>
       <c r="D10" t="str">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>6</v>
       </c>
       <c r="C11" t="str">
-        <v>F02</v>
+        <v>F02_TC06</v>
       </c>
       <c r="D11" t="str">
         <v>1</v>
@@ -1475,7 +1475,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="str">
-        <v>F02</v>
+        <v>F02_TC07</v>
       </c>
       <c r="D12" t="str">
         <v>1</v>
@@ -1501,7 +1501,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="str">
-        <v>F02</v>
+        <v>F02_TC08</v>
       </c>
       <c r="D13" t="str">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>9</v>
       </c>
       <c r="C14" t="str">
-        <v>F02</v>
+        <v>F02_TC09</v>
       </c>
       <c r="D14" t="str">
         <v>1</v>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="C15" t="str">
-        <v>F02</v>
+        <v>F02_TC10</v>
       </c>
       <c r="D15" t="str">
         <v>1</v>
